--- a/Documentacion Sprint (01 - 11)/Sprint 8 documentacion/Sprint_08_Backlog_ICARO.xlsx
+++ b/Documentacion Sprint (01 - 11)/Sprint 8 documentacion/Sprint_08_Backlog_ICARO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 8 documentacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentacion Sprint (01 - 11)\Sprint 8 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1517CFA-EB60-47FD-A6CD-5967E3503A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBC7EFA-E83D-409E-806E-C6AD0DC15E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPRINT BACKLOG" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="239">
   <si>
     <t>ID</t>
   </si>
@@ -905,9 +905,6 @@
     <t>backend/src/routes/bodega.routes.js, backend/src/controllers/bodega.controller.js, backend/src/services/bodega.service.js, backend/tests/sprint8_bodega_inventario.test.js – CP-189 a CP-193</t>
   </si>
   <si>
-    <t>RESUMEN DE VELOCIDAD — Sprint 06</t>
-  </si>
-  <si>
     <t>Métrica</t>
   </si>
   <si>
@@ -1122,13 +1119,19 @@
   </si>
   <si>
     <t>Documento de resultados de pruebas del sprint</t>
+  </si>
+  <si>
+    <t>Los estados presentados en este documento corresponden al estado del Product/Sprint Backlog al cierre del Sprint respectivo. Debido a la naturaleza iterativa e incremental del proyecto, los elementos identificados como pendientes, diferidos o parcialmente implementados pudieron ser desarrollados y completados en sprints posteriores. Para conocer el estado definitivo de cada historia de usuario o historia técnica, debe consultarse el Product Backlog Consolidado al cierre del proyecto.</t>
+  </si>
+  <si>
+    <t>RESUMEN DE VELOCIDAD — Sprint 08</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1247,8 +1250,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1297,8 +1307,13 @@
         <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1336,9 +1351,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1387,74 +1418,77 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Notas" xfId="1" builtinId="10"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -1864,7 +1898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5300126-01E7-4AE7-AF61-110B8C60A0AE}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="8" max="8" width="13.140625" customWidth="1"/>
@@ -1875,124 +1909,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
       <c r="G3" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
     </row>
     <row r="4" spans="1:12" ht="24">
       <c r="A4" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="30">
         <v>46174</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
       <c r="G4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="30">
         <v>46178</v>
       </c>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
     </row>
     <row r="5" spans="1:12" ht="107.25" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
       <c r="G5" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
     </row>
     <row r="6" spans="1:12" ht="24">
       <c r="A6" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
       <c r="G6" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
     </row>
     <row r="7" spans="1:12" ht="30">
       <c r="A7" s="1" t="s">
@@ -2261,13 +2295,13 @@
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="7">
         <v>44</v>
       </c>
@@ -2280,19 +2314,85 @@
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
     </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="A14:E14"/>
+  <mergeCells count="12">
+    <mergeCell ref="A16:G22"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2311,532 +2411,532 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="18" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="21" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="18" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="21" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="21" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="18" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="21" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="18" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="36" t="s">
+      <c r="E13" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="18" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="21" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="36" t="s">
+      <c r="E15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="18" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="38" t="s">
+      <c r="F16" s="21" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="18" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="21" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A19" s="34" t="s">
+      <c r="A19" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A20" s="37" t="s">
+      <c r="A20" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="38" t="s">
+      <c r="F20" s="21" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B21" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="36" t="s">
+      <c r="E21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="18" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="38" t="s">
+      <c r="F22" s="21" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B23" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="35" t="s">
+      <c r="D23" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="36" t="s">
+      <c r="E23" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="18" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A24" s="37" t="s">
+      <c r="A24" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="38" t="s">
+      <c r="F24" s="21" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D25" s="35" t="s">
+      <c r="D25" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="E25" s="36" t="s">
+      <c r="E25" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="18" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E26" s="36" t="s">
+      <c r="E26" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="21" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="14.1" customHeight="1">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D27" s="35" t="s">
+      <c r="D27" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E27" s="36" t="s">
+      <c r="E27" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="35" t="s">
+      <c r="F27" s="18" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2859,30 +2959,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
+      <c r="A1" s="37" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B3" s="8">
         <v>44</v>
@@ -2891,12 +2991,12 @@
         <v>44</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B4" s="8">
         <v>5</v>
@@ -2905,12 +3005,12 @@
         <v>5</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B5" s="8">
         <v>1</v>
@@ -2924,7 +3024,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B6" s="8">
         <v>6</v>
@@ -2933,12 +3033,12 @@
         <v>6</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B7" s="8">
         <v>6</v>
@@ -2952,7 +3052,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B8" s="8">
         <v>0</v>
@@ -2961,12 +3061,12 @@
         <v>0</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B9" s="8">
         <v>0</v>
@@ -2975,12 +3075,12 @@
         <v>0</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B10" s="8">
         <v>44</v>
@@ -2989,12 +3089,12 @@
         <v>44</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B11" s="9">
         <v>1</v>
@@ -3003,12 +3103,12 @@
         <v>1</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B12" s="8">
         <v>25</v>
@@ -3017,12 +3117,12 @@
         <v>25</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B13" s="9">
         <v>1</v>
@@ -3031,12 +3131,12 @@
         <v>1</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B14" s="8">
         <v>193</v>
@@ -3045,7 +3145,7 @@
         <v>193</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3069,21 +3169,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
+      <c r="A1" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="11" t="s">
         <v>194</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3091,10 +3191,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>196</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3102,153 +3202,153 @@
         <v>19</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>198</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="C5" s="13" t="s">
         <v>201</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="C6" s="15" t="s">
         <v>204</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="13" t="s">
         <v>207</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="C8" s="15" t="s">
         <v>210</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="13" t="s">
         <v>213</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="C10" s="15" t="s">
         <v>216</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="C11" s="13" t="s">
         <v>219</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="C12" s="15" t="s">
         <v>222</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="C13" s="13" t="s">
         <v>225</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="C14" s="15" t="s">
         <v>228</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>116</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="C16" s="15" t="s">
         <v>233</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="C17" s="13" t="s">
         <v>236</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>237</v>
       </c>
     </row>
   </sheetData>
